--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,46 +1103,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R5" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1177,17 +1172,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1196,11 +1187,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1213,12 +1199,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1239,7 +1225,7 @@
         <v>122779255</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1372,10 +1358,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779254</v>
+        <v>122779215</v>
       </c>
       <c r="B7" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1388,30 +1374,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1419,10 +1401,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506701</v>
+        <v>506627</v>
       </c>
       <c r="R7" t="n">
-        <v>7053096</v>
+        <v>7053057</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1484,12 +1466,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1507,10 +1489,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779215</v>
+        <v>122779188</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1523,37 +1505,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506627</v>
+        <v>506664</v>
       </c>
       <c r="R8" t="n">
-        <v>7053057</v>
+        <v>7053016</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1588,13 +1579,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1603,6 +1598,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -938,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779089</v>
+        <v>122779255</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,46 +954,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506686</v>
+        <v>506701</v>
       </c>
       <c r="R4" t="n">
-        <v>7053093</v>
+        <v>7053096</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1028,17 +1019,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1049,7 +1036,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1064,12 +1051,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1087,10 +1074,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779254</v>
+        <v>122779089</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,41 +1090,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506701</v>
+        <v>506686</v>
       </c>
       <c r="R5" t="n">
-        <v>7053096</v>
+        <v>7053093</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1172,13 +1164,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1187,6 +1183,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1199,12 +1200,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1222,7 +1223,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779255</v>
+        <v>122779215</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1265,10 +1266,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506701</v>
+        <v>506627</v>
       </c>
       <c r="R6" t="n">
-        <v>7053096</v>
+        <v>7053057</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1316,11 +1317,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1358,10 +1354,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779215</v>
+        <v>122779188</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1374,37 +1370,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506627</v>
+        <v>506664</v>
       </c>
       <c r="R7" t="n">
-        <v>7053057</v>
+        <v>7053016</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1439,13 +1444,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1454,6 +1463,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1466,12 +1480,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1489,10 +1503,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1505,46 +1519,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R8" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1579,17 +1588,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1598,11 +1603,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -938,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779255</v>
+        <v>122779188</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,37 +954,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R4" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1019,13 +1028,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1036,7 +1049,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1051,12 +1064,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1074,10 +1087,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779089</v>
+        <v>122779254</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1090,46 +1103,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506686</v>
+        <v>506701</v>
       </c>
       <c r="R5" t="n">
-        <v>7053093</v>
+        <v>7053096</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1164,17 +1172,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1183,11 +1187,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1200,12 +1199,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1223,7 +1222,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779215</v>
+        <v>122779255</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1266,10 +1265,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506627</v>
+        <v>506701</v>
       </c>
       <c r="R6" t="n">
-        <v>7053057</v>
+        <v>7053096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1317,6 +1316,11 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1354,10 +1358,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779188</v>
+        <v>122779215</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1370,46 +1374,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506664</v>
+        <v>506627</v>
       </c>
       <c r="R7" t="n">
-        <v>7053016</v>
+        <v>7053057</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1444,17 +1439,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1463,11 +1454,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1480,12 +1466,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1503,10 +1489,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779254</v>
+        <v>122779089</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1519,41 +1505,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506701</v>
+        <v>506686</v>
       </c>
       <c r="R8" t="n">
-        <v>7053096</v>
+        <v>7053093</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1588,13 +1579,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1603,6 +1598,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -938,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,46 +954,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R4" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1028,17 +1023,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1047,11 +1038,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1064,12 +1050,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1087,10 +1073,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779254</v>
+        <v>122779089</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,41 +1089,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506701</v>
+        <v>506686</v>
       </c>
       <c r="R5" t="n">
-        <v>7053096</v>
+        <v>7053093</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1172,13 +1163,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1187,6 +1182,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779255</v>
+        <v>122779188</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1238,37 +1238,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R6" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1303,13 +1312,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1320,7 +1333,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1335,12 +1348,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1489,10 +1502,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779089</v>
+        <v>122779255</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1505,46 +1518,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506686</v>
+        <v>506701</v>
       </c>
       <c r="R8" t="n">
-        <v>7053093</v>
+        <v>7053096</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1579,17 +1583,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122768066</v>
+        <v>122779254</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,57 +817,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506635</v>
+        <v>506701</v>
       </c>
       <c r="R3" t="n">
-        <v>7053059</v>
+        <v>7053096</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,17 +886,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Synobservation av en hona som födosökte på en ca 20 meter hög stående död gran, både på stammen och en gren. Hörde även trummande av två spettar innan dess som antyder att det även kan finnas en hane av tretåig hackspett på/kring fyndplatsen. Dessutom rikligt med stående grov granved här (upp till 50 cm BHD) som indikerar mycket höga livsmiljövärden för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -918,9 +901,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779254</v>
+        <v>122779089</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,41 +952,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506701</v>
+        <v>506686</v>
       </c>
       <c r="R4" t="n">
-        <v>7053096</v>
+        <v>7053093</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,13 +1026,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1038,6 +1045,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1050,12 +1062,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1073,7 +1085,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779089</v>
+        <v>122779188</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1125,10 +1137,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506686</v>
+        <v>506664</v>
       </c>
       <c r="R5" t="n">
-        <v>7053093</v>
+        <v>7053016</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1165,7 +1177,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1222,10 +1234,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779188</v>
+        <v>122779215</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1238,46 +1250,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506664</v>
+        <v>506627</v>
       </c>
       <c r="R6" t="n">
-        <v>7053016</v>
+        <v>7053057</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1312,17 +1315,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1331,11 +1330,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1348,12 +1342,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1371,7 +1365,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779215</v>
+        <v>122779255</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1414,10 +1408,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506627</v>
+        <v>506701</v>
       </c>
       <c r="R7" t="n">
-        <v>7053057</v>
+        <v>7053096</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1465,6 +1459,11 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1502,14 +1501,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779255</v>
+        <v>122768066</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1518,40 +1517,57 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506701</v>
+        <v>506635</v>
       </c>
       <c r="R8" t="n">
-        <v>7053096</v>
+        <v>7053059</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1583,13 +1599,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Synobservation av en hona som födosökte på en ca 20 meter hög stående död gran, både på stammen och en gren. Hörde även trummande av två spettar innan dess som antyder att det även kan finnas en hane av tretåig hackspett på/kring fyndplatsen. Dessutom rikligt med stående grov granved här (upp till 50 cm BHD) som indikerar mycket höga livsmiljövärden för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1600,27 +1620,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122779254</v>
+        <v>122779188</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,41 +817,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R3" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,13 +891,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,6 +910,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>gran</t>
@@ -913,12 +927,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779089</v>
+        <v>122779255</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,46 +966,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506686</v>
+        <v>506701</v>
       </c>
       <c r="R4" t="n">
-        <v>7053093</v>
+        <v>7053096</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,17 +1031,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1047,7 +1048,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1062,12 +1063,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1085,10 +1086,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779188</v>
+        <v>122779215</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,46 +1102,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506664</v>
+        <v>506627</v>
       </c>
       <c r="R5" t="n">
-        <v>7053016</v>
+        <v>7053057</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1175,17 +1167,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1194,11 +1182,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1211,12 +1194,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1234,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779215</v>
+        <v>122779089</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1250,37 +1233,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506627</v>
+        <v>506686</v>
       </c>
       <c r="R6" t="n">
-        <v>7053057</v>
+        <v>7053093</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1315,13 +1307,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1330,6 +1326,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1342,12 +1343,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1365,10 +1366,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779255</v>
+        <v>122779254</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,26 +1382,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1461,11 +1466,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,46 +817,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R3" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,17 +886,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,11 +901,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>gran</t>
@@ -927,12 +913,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779255</v>
+        <v>122779188</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,37 +952,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R4" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1031,13 +1026,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1048,7 +1047,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1063,12 +1062,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1086,7 +1085,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779215</v>
+        <v>122779255</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1129,10 +1128,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506627</v>
+        <v>506701</v>
       </c>
       <c r="R5" t="n">
-        <v>7053057</v>
+        <v>7053096</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1180,6 +1179,11 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1366,10 +1370,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779254</v>
+        <v>122779215</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,30 +1386,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506701</v>
+        <v>506627</v>
       </c>
       <c r="R7" t="n">
-        <v>7053096</v>
+        <v>7053057</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -1221,10 +1221,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779089</v>
+        <v>122779215</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,46 +1237,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506686</v>
+        <v>506627</v>
       </c>
       <c r="R6" t="n">
-        <v>7053093</v>
+        <v>7053057</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1311,17 +1302,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1330,11 +1317,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1347,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1370,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779215</v>
+        <v>122779089</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1386,37 +1368,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506627</v>
+        <v>506686</v>
       </c>
       <c r="R7" t="n">
-        <v>7053057</v>
+        <v>7053093</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1451,13 +1442,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1466,6 +1461,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122779254</v>
+        <v>122779089</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,41 +817,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506701</v>
+        <v>506686</v>
       </c>
       <c r="R3" t="n">
-        <v>7053096</v>
+        <v>7053093</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,13 +891,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,6 +910,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>gran</t>
@@ -913,12 +927,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779188</v>
+        <v>122779215</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,46 +966,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506664</v>
+        <v>506627</v>
       </c>
       <c r="R4" t="n">
-        <v>7053016</v>
+        <v>7053057</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,17 +1031,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1045,11 +1046,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1062,12 +1058,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1221,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779215</v>
+        <v>122779254</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,26 +1233,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506627</v>
+        <v>506701</v>
       </c>
       <c r="R6" t="n">
-        <v>7053057</v>
+        <v>7053096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779089</v>
+        <v>122779188</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506686</v>
+        <v>506664</v>
       </c>
       <c r="R7" t="n">
-        <v>7053093</v>
+        <v>7053016</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -1217,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779254</v>
+        <v>122779188</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,41 +1233,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R6" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1302,13 +1307,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1317,6 +1326,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1329,12 +1343,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1352,10 +1366,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1368,46 +1382,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R7" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1442,17 +1451,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1461,11 +1466,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -1217,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,46 +1233,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R6" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1307,17 +1302,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1326,11 +1317,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1343,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1366,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779254</v>
+        <v>122779188</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,41 +1368,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R7" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1451,13 +1442,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1466,6 +1461,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122779089</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>122779215</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>122779255</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90973</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,46 +1233,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R6" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1307,17 +1302,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1326,11 +1317,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1343,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1366,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779254</v>
+        <v>122779188</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,41 +1368,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R7" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1451,13 +1442,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1466,6 +1461,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
         <v>122768066</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -950,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779215</v>
+        <v>122779255</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506627</v>
+        <v>506701</v>
       </c>
       <c r="R4" t="n">
-        <v>7053057</v>
+        <v>7053096</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1044,6 +1044,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1081,10 +1086,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779255</v>
+        <v>122779254</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,26 +1102,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1177,11 +1186,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1194,12 +1198,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1217,10 +1221,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779254</v>
+        <v>122779215</v>
       </c>
       <c r="B6" t="n">
-        <v>90973</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,30 +1237,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506701</v>
+        <v>506627</v>
       </c>
       <c r="R6" t="n">
-        <v>7053096</v>
+        <v>7053057</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122779089</v>
+        <v>122779215</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,46 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506686</v>
+        <v>506627</v>
       </c>
       <c r="R3" t="n">
-        <v>7053093</v>
+        <v>7053057</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,17 +882,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,11 +897,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>gran</t>
@@ -927,12 +909,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779255</v>
+        <v>122779254</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>90981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,26 +948,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1046,11 +1032,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1063,12 +1044,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1086,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779254</v>
+        <v>122779255</v>
       </c>
       <c r="B5" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,30 +1083,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1186,6 +1163,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1198,12 +1180,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1221,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779215</v>
+        <v>122779188</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,37 +1219,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506627</v>
+        <v>506664</v>
       </c>
       <c r="R6" t="n">
-        <v>7053057</v>
+        <v>7053016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1302,13 +1293,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1317,6 +1312,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122779188</v>
+        <v>122779089</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506664</v>
+        <v>506686</v>
       </c>
       <c r="R7" t="n">
-        <v>7053016</v>
+        <v>7053093</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122779215</v>
+        <v>122779254</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>90984</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,26 +817,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506627</v>
+        <v>506701</v>
       </c>
       <c r="R3" t="n">
-        <v>7053057</v>
+        <v>7053096</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,12 +913,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122779254</v>
+        <v>122779255</v>
       </c>
       <c r="B4" t="n">
-        <v>90981</v>
+        <v>78775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,30 +952,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1032,6 +1032,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1044,12 +1049,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1067,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779255</v>
+        <v>122779188</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,37 +1088,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R5" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1148,13 +1162,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1165,7 +1183,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1180,12 +1198,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1221,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779188</v>
+        <v>122779215</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,46 +1237,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506664</v>
+        <v>506627</v>
       </c>
       <c r="R6" t="n">
-        <v>7053016</v>
+        <v>7053057</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1293,17 +1302,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1312,11 +1317,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>122768066</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1636,6 +1636,155 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123771494</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57487</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>506638</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7053070</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>122768066</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>123771494</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>122768066</v>
       </c>
       <c r="B8" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>123771494</v>
       </c>
       <c r="B9" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -1504,12 +1504,7 @@
         <v>122768066</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90798946</v>
+        <v>90798941</v>
       </c>
       <c r="B2" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222741</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506548.0380416627</v>
+        <v>506608</v>
       </c>
       <c r="R2" t="n">
-        <v>7053008.055698043</v>
+        <v>7053126</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2019-08-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,6 +760,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -801,46 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122779254</v>
+        <v>122779215</v>
       </c>
       <c r="B3" t="n">
-        <v>90984</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506701</v>
+        <v>506627</v>
       </c>
       <c r="R3" t="n">
-        <v>7053096</v>
+        <v>7053057</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -913,12 +894,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,16 +920,11 @@
         <v>122779255</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1072,65 +1048,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122779188</v>
+        <v>90798816</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Vargsundsvägen-Brattmyrarna_NO, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506664</v>
+        <v>506741</v>
       </c>
       <c r="R5" t="n">
-        <v>7053016</v>
+        <v>7053091</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1154,17 +1113,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,60 +1130,44 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Möjlig kalkbarrskog</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Rönn</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122779215</v>
+        <v>122768066</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,40 +1175,57 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506627</v>
+        <v>506635</v>
       </c>
       <c r="R6" t="n">
-        <v>7053057</v>
+        <v>7053059</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1302,13 +1257,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Synobservation av en hona som födosökte på en ca 20 meter hög stående död gran, både på stammen och en gren. Hörde även trummande av två spettar innan dess som antyder att det även kan finnas en hane av tretåig hackspett på/kring fyndplatsen. Dessutom rikligt med stående grov granved här (upp till 50 cm BHD) som indikerar mycket höga livsmiljövärden för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1317,24 +1276,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1355,12 +1299,7 @@
         <v>122779089</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1501,10 +1440,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122768066</v>
+        <v>122779188</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,20 +1468,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1552,17 +1483,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506635</v>
+        <v>506664</v>
       </c>
       <c r="R8" t="n">
-        <v>7053059</v>
+        <v>7053016</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1527,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Synobservation av en hona som födosökte på en ca 20 meter hög stående död gran, både på stammen och en gren. Hörde även trummande av två spettar innan dess som antyder att det även kan finnas en hane av tretåig hackspett på/kring fyndplatsen. Dessutom rikligt med stående grov granved här (upp till 50 cm BHD) som indikerar mycket höga livsmiljövärden för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1616,6 +1547,26 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1636,12 +1587,7 @@
         <v>123771494</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1779,6 +1725,117 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>90798946</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vargsundsvägen-Brattmyrarna_NO, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>506548</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7053008</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-08-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-08-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2759-2025 artfynd.xlsx
+++ b/artfynd/A 2759-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90798946</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90798941</t>
         </is>
       </c>
     </row>
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779215</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779255</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90798816</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1404,6 +1434,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122768066</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1548,6 +1583,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779089</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1692,6 +1732,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779188</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1836,8 +1881,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771494</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>